--- a/stories/arbres/ATOM-TMP.MOI.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Eliott est à la cuisine. Maman accroche un calendrier. Maman dit : il y a douze mois. Janvier, février, mars. Avril, mai, juin. Juillet, août, septembre. Octobre, novembre, décembre. Eliott pose le doigt. Maman dit : mars. L'anniversaire d'Eliott est en mars. Eliott répète : douze mois. Un anniversaire a un mois.</t>
+          <t>Eliott est à la cuisine. Maman accroche un calendrier. Il y a douze mois. Janvier, février, mars. Avril, mai, juin. Juillet, août, septembre. Octobre, novembre, décembre. Eliott pose le doigt. Mars. L'anniversaire d'Eliott est en mars. Eliott répète : douze mois. Un anniversaire a un mois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Eliott est à la cuisine. Maman accroche un calendrier.
+maman|Il y a douze mois. Janvier, février, mars. Avril, mai, juin. Juillet, août, septembre. Octobre, novembre, décembre.
+narrateur|Eliott pose le doigt.
+maman|Mars. L'anniversaire d'Eliott est en mars.
+narrateur|Eliott répète : douze mois. Un anniversaire a un mois.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Eliott a un mois sur le calendrier. Pourquoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Eliott a entendu les douze mois. Son anniversaire est en mars.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le crayon. Eliott touche une étoile.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MOI.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Eliott répète : douze mois. Un anniversaire a un mois.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Eliott a un mois sur le calendrier. Pourquoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Eliott a entendu les douze mois. Son anniversaire est en mars.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Maman range le crayon. Eliott touche une étoile.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.MOI.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eliott entend les douze mois</t>
+          <t>La soupe de novembre</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou veut la soupe de courge. Maman dit novembre. Les pages du calendrier collent. Chouchou essuie, trouve novembre, et la casserole chante.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Eliott est à la cuisine. Maman accroche un calendrier. Il y a douze mois. Janvier, février, mars. Avril, mai, juin. Juillet, août, septembre. Octobre, novembre, décembre. Eliott pose le doigt. Mars. L'anniversaire d'Eliott est en mars. Eliott répète : douze mois. Un anniversaire a un mois.</t>
+          <t>La vitre de la cuisine a des gouttes. Ça sent l'écorce d'orange, un peu. Une courge orange attend sur le bois. Elle est lourde, presque ronde. Un couteau repose près de l'évier. Maman essuie une miette de pain. Je veux la soupe, maman. La soupe de courge ? Oui. Celle qui est douce. On la fait en novembre. Un calendrier pend près de la fenêtre. Les pages sont épaisses, un peu jaunes. Un crayon rouge est coincé dessus. En ce moment, Chouchou touche une page. Le papier est rêche sous son doigt. Où est novembre ? Cherche la page, tout doucement. Chouchou tourne une feuille. Une image d'arbre nu apparaît. C'est novembre ? Ça, c'est octobre. Les feuilles tombent encore. Chouchou a les doigts un peu mouillés. Elle a touché la courge, avant. Une goutte reste sur le pouce. Elle tourne encore. Deux pages collent, bien fort. Elles ne viennent pas. Tes doigts sont mouillés, Chouchou. Le papier fait un bruit mou. Chh. Les deux pages restent ensemble. Une image d'étoile passe trop vite. J'ai sauté un mois ? Peut-être. On essuie, puis on cherche. Maman tend un linge tiède. Le linge sent le savon de vaisselle. Chouchou frotte ses paumes. Le linge devient un peu orange. Mes mains sont sèches. Merci. Tu peux décoller, maintenant ? Chouchou souffle sur le bord. Elle pince le coin, tout doux. Le papier se sépare, lentement. Une page cachée apparaît. Il y a une petite courge dessinée. Novembre ! Oui. C'est le mois de la soupe. Chouchou pose le crayon rouge. Elle fait un rond sur novembre. Le crayon gratte, tout léger. On coupe la courge ? Oui. Tu tiens le saladier ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Eliott est à la cuisine. Maman accroche un calendrier. Maman dit : il y a &lt;emphasis level="moderate"&gt;douze&lt;/emphasis&gt; mois. Janvier, février, mars. Avril, mai, juin. Juillet, août, septembre. Octobre, novembre, décembre. Eliott pose le doigt. Maman dit : mars. L'anniversaire d'Eliott est en mars. Eliott répète : douze mois. Un anniversaire a un mois.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vitre de la cuisine a des gouttes. Ça sent l'écorce d'orange, un peu. Une courge orange attend sur le bois. Elle est lourde, presque ronde. Un couteau repose près de l'évier. Maman essuie une miette de pain. Je veux la soupe, maman. La soupe de courge ? Oui. Celle qui est douce. On la fait en novembre. Un calendrier pend près de la fenêtre. Les pages sont épaisses, un peu jaunes. Un crayon rouge est coincé dessus. En ce moment, Chouchou touche une page. Le papier est rêche sous son doigt. Où est novembre ? Cherche la page, tout doucement. Chouchou tourne une feuille. Une image d'arbre nu apparaît. C'est novembre ? Ça, c'est octobre. Les feuilles tombent encore. Chouchou a les doigts un peu mouillés. Elle a touché la courge, avant. Une goutte reste sur le pouce. Elle tourne encore. Deux pages collent, bien fort. Elles ne viennent pas. Tes doigts sont mouillés, Chouchou. Le papier fait un bruit mou. Chh. Les deux pages restent ensemble. Une image d'étoile passe trop vite. J'ai sauté un mois ? Peut-être. On essuie, puis on cherche. Maman tend un linge tiède. Le linge sent le savon de vaisselle. Chouchou frotte ses paumes. Le linge devient un peu orange. Mes mains sont sèches. Merci. Tu peux décoller, maintenant ? Chouchou souffle sur le bord. Elle pince le coin, tout doux. Le papier se sépare, lentement. Une page cachée apparaît. Il y a une petite courge dessinée. Novembre ! Oui. C'est le mois de la soupe. Chouchou pose le crayon rouge. Elle fait un rond sur novembre. Le crayon gratte, tout léger. On coupe la courge ? Oui. Tu tiens le saladier ?</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,66 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Eliott est à la cuisine. Maman accroche un calendrier.
-maman|Il y a douze mois. Janvier, février, mars. Avril, mai, juin. Juillet, août, septembre. Octobre, novembre, décembre.
-narrateur|Eliott pose le doigt.
-maman|Mars. L'anniversaire d'Eliott est en mars.
-narrateur|Eliott répète : douze mois. Un anniversaire a un mois.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La vitre de la cuisine a des gouttes.
+narrateur|Ça sent l'écorce d'orange, un peu.
+narrateur|Une courge orange attend sur le bois.
+narrateur|Elle est lourde, presque ronde.
+narrateur|Un couteau repose près de l'évier.
+narrateur|Maman essuie une miette de pain.
+enfant-f|Je veux la soupe, maman.
+maman|La soupe de courge ?
+enfant-f|Oui.
+enfant-f|Celle qui est douce.
+maman|On la fait en novembre.
+narrateur|Un calendrier pend près de la fenêtre.
+narrateur|Les pages sont épaisses, un peu jaunes.
+narrateur|Un crayon rouge est coincé dessus.
+narrateur|En ce moment, Chouchou touche une page.
+narrateur|Le papier est rêche sous son doigt.
+enfant-f|Où est novembre ?
+maman|Cherche la page, tout doucement.
+narrateur|Chouchou tourne une feuille.
+narrateur|Une image d'arbre nu apparaît.
+enfant-f|C'est novembre ?
+maman|Ça, c'est octobre.
+maman|Les feuilles tombent encore.
+narrateur|Chouchou a les doigts un peu mouillés.
+narrateur|Elle a touché la courge, avant.
+narrateur|Une goutte reste sur le pouce.
+narrateur|Elle tourne encore.
+narrateur|Deux pages collent, bien fort.
+enfant-f|Elles ne viennent pas.
+maman|Tes doigts sont mouillés, Chouchou.
+narrateur|Le papier fait un bruit mou.
+narrateur|Chh.
+narrateur|Les deux pages restent ensemble.
+narrateur|Une image d'étoile passe trop vite.
+enfant-f|J'ai sauté un mois ?
+maman|Peut-être.
+maman|On essuie, puis on cherche.
+narrateur|Maman tend un linge tiède.
+narrateur|Le linge sent le savon de vaisselle.
+narrateur|Chouchou frotte ses paumes.
+narrateur|Le linge devient un peu orange.
+enfant-f|Mes mains sont sèches.
+maman|Merci.
+maman|Tu peux décoller, maintenant ?
+narrateur|Chouchou souffle sur le bord.
+narrateur|Elle pince le coin, tout doux.
+narrateur|Le papier se sépare, lentement.
+narrateur|Une page cachée apparaît.
+narrateur|Il y a une petite courge dessinée.
+enfant-f|Novembre !
+maman|Oui.
+maman|C'est le mois de la soupe.
+narrateur|Chouchou pose le crayon rouge.
+narrateur|Elle fait un rond sur novembre.
+narrateur|Le crayon gratte, tout léger.
+enfant-f|On coupe la courge ?
+maman|Oui.
+maman|Tu tiens le saladier ?</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1408,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Eliott a un mois sur le calendrier. Pourquoi ?</t>
+          <t>Chouchou a trouvé un mois pour la soupe. Lequel ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Eliott a un mois sur le calendrier. Pourquoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a trouvé un mois pour la soupe. Lequel ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1359,12 +1423,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>mars</t>
+          <t>novembre</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>mars | un mois | anniversaire | douze mois</t>
+          <t>novembre | en novembre | le mois | la soupe | courge</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1379,7 +1443,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il y a douze mois. Lequel est celui d'Eliott ?</t>
+          <t>La soupe de courge, c'est en novembre. Quel mois ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1428,7 +1492,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1500,10 +1564,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Eliott a un mois sur le calendrier. Pourquoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Chouchou a trouvé un mois pour la soupe.
+narrateur|Lequel ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,12 +1592,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Eliott a entendu les douze mois. Son anniversaire est en mars.</t>
+          <t>Le couteau tape le bois, tout doux. Toc. La courge s'ouvre, orange dedans. Elle est comme un soleil. On met les morceaux dans la casserole. Chouchou pousse un cube orange. Il glisse, puis tombe dans l'eau. Ça sent déjà le chaud, un peu. Novembre est sur le calendrier. Et la soupe est dans la casserole. Les deux ensemble. Une bulle monte, toute ronde. Chouchou regarde novembre, puis la vapeur.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Eliott a entendu les &lt;emphasis level="moderate"&gt;douze&lt;/emphasis&gt; mois. Son anniversaire est en mars.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le couteau tape le bois, tout doux. Toc. La courge s'ouvre, orange dedans. Elle est comme un soleil. On met les morceaux dans la casserole. Chouchou pousse un cube orange. Il glisse, puis tombe dans l'eau. Ça sent déjà le chaud, un peu. Novembre est sur le calendrier. Et la soupe est dans la casserole. Les deux ensemble. Une bulle monte, toute ronde. Chouchou regarde novembre, puis la vapeur.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1596,7 +1660,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1672,10 +1736,21 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Eliott a entendu les douze mois. Son anniversaire est en mars.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le couteau tape le bois, tout doux.
+narrateur|Toc.
+narrateur|La courge s'ouvre, orange dedans.
+enfant-f|Elle est comme un soleil.
+maman|On met les morceaux dans la casserole.
+narrateur|Chouchou pousse un cube orange.
+narrateur|Il glisse, puis tombe dans l'eau.
+narrateur|Ça sent déjà le chaud, un peu.
+maman|Novembre est sur le calendrier.
+enfant-f|Et la soupe est dans la casserole.
+maman|Les deux ensemble.
+narrateur|Une bulle monte, toute ronde.
+narrateur|Chouchou regarde novembre, puis la vapeur.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,12 +1775,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le crayon. Eliott touche une étoile.</t>
+          <t>Maman verse la soupe dans deux bols. La vapeur fait un nuage bas. Chouchou souffle, tout long. Elle est douce. C'est la soupe de novembre. Le crayon rouge reste sur la page. La petite courge dessinée brille un peu. Tu as décollé les pages. Et j'ai trouvé le mois.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range le crayon. Eliott touche une étoile.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman verse la soupe dans deux bols. La vapeur fait un nuage bas. Chouchou souffle, tout long. Elle est douce. C'est la soupe de novembre. Le crayon rouge reste sur la page. La petite courge dessinée brille un peu. Tu as décollé les pages. Et j'ai trouvé le mois.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1768,7 +1843,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1836,10 +1911,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le crayon. Eliott touche une étoile.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman verse la soupe dans deux bols.
+narrateur|La vapeur fait un nuage bas.
+narrateur|Chouchou souffle, tout long.
+enfant-f|Elle est douce.
+maman|C'est la soupe de novembre.
+narrateur|Le crayon rouge reste sur la page.
+narrateur|La petite courge dessinée brille un peu.
+maman|Tu as décollé les pages.
+enfant-f|Et j'ai trouvé le mois.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1864,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le bol tiédit sous ses mains. La vitre a encore des gouttes. Novembre est ouvert, tout grand. Encore une cuillère. Oui. La courge sent le bois et le chaud. Chouchou pose la cuillère, enfin rassasiée.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bol tiédit sous ses mains. La vitre a encore des gouttes. Novembre est ouvert, tout grand. Encore une cuillère. Oui. La courge sent le bois et le chaud. Chouchou pose la cuillère, enfin rassasiée.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1925,14 +2007,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2004,10 +2086,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le bol tiédit sous ses mains.
+narrateur|La vitre a encore des gouttes.
+narrateur|Novembre est ouvert, tout grand.
+enfant-f|Encore une cuillère.
+maman|Oui.
+narrateur|La courge sent le bois et le chaud.
+narrateur|Chouchou pose la cuillère, enfin rassasiée.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2151,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MOI.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine, calendrier mural, courge sur la table</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Eliott, maman</t>
+          <t>Chouchou, maman</t>
         </is>
       </c>
     </row>
